--- a/MATH/M10/bus123-math-m10-l01-starter.xlsx
+++ b/MATH/M10/bus123-math-m10-l01-starter.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R4b551ac4a2654db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R51529abdcd4f41ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rfd4123af5b4e4ea7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R7ce5016f38364bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R9cba5cd439d845d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R0d6fd31106e84e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R992c3ac4f69147b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R2915aa483d2d4bf2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,13 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <x:numFmt numFmtId="165" formatCode="0.0"/>
     <x:numFmt numFmtId="166" formatCode="$#,##0"/>
     <x:numFmt numFmtId="167" formatCode="0.0%"/>
+    <x:numFmt numFmtId="200" formatCode="&quot;$&quot;#,##0"/>
+    <x:numFmt numFmtId="201" formatCode="0.00%"/>
+    <x:numFmt numFmtId="202" formatCode="&quot;$&quot;#,##0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="20">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -52,8 +56,95 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF4A5567"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="JetBrains Mono"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF4A5567"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0E1116"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF4A5567"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0E1116"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF355773"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="31">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -80,8 +171,133 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0E1116"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF355773"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3EC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2EEE5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -129,11 +345,114 @@
         <x:color rgb="FFD9E2D0"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFD7DECF"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="364">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -176,10 +495,962 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="13" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="19" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="13" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="13" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="14" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="19" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="18" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="13" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="19" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="19" fillId="18" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="22" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="23" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="13" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="25" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="24" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="19" fillId="23" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="27" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="28" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="29" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="17" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="28" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="13" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="13" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="13" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="14" fillId="30" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="14" fillId="29" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="19" fillId="28" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="10">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4A7C5E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4A7C5E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4A7C5E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4A7C5E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill>
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF4A7C5E"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2F0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF9C4A2B"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFCE4D6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
   <x:colors>
     <x:indexedColors>
       <x:rgbColor rgb="00000000"/>
@@ -520,7 +1791,7 @@
       <x:c r="H4" s="15" t="n"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="4" t="inlineStr">
+      <x:c r="A5" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1. Open the slide deck and pause when you see a Live You Try It slide.</x:t>
         </x:is>
@@ -534,7 +1805,7 @@
       <x:c r="H5" s="15" t="n"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="4" t="inlineStr">
+      <x:c r="A6" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2. In Live You Try It, enter the slide givens into the yellow input cells first.</x:t>
         </x:is>
@@ -548,7 +1819,7 @@
       <x:c r="H6" s="15" t="n"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="4" t="inlineStr">
+      <x:c r="A7" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3. Build formulas by referencing those input cells. The feedback column self-checks your practice.</x:t>
         </x:is>
@@ -561,11 +1832,9 @@
       <x:c r="G7" s="14" t="n"/>
       <x:c r="H7" s="15" t="n"/>
     </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4. Complete Class Challenge after live practice. Read each scenario, extract inputs, and enter final numeric answers.</x:t>
-        </x:is>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="16" t="str">
+        <x:v>4. Begin Class Challenge in class, then finish it for homework. Build linked calculations, comparison tests, and a defensible recommendation.</x:v>
       </x:c>
       <x:c r="B8" s="14" t="n"/>
       <x:c r="C8" s="14" t="n"/>
@@ -576,7 +1845,7 @@
       <x:c r="H8" s="15" t="n"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="4" t="inlineStr">
+      <x:c r="A9" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5. FormulaReferenceCard is a syntax helper. It is not a substitute for choosing the right inputs.</x:t>
         </x:is>
@@ -621,51 +1890,45 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
-      <x:c r="A14" s="4" t="inlineStr">
+      <x:c r="A14" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Live You Try It</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="4" t="inlineStr">
+      <x:c r="B14" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Short Excel pauses tied to worked examples in the slide deck; self-graded with hints and feedback.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="4" t="inlineStr">
+      <x:c r="C14" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Practice only</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="15" ht="44" customHeight="1">
-      <x:c r="A15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Class Challenge</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Next-level scenario table with 15 final-answer questions.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Only graded tab</x:t>
-        </x:is>
+      <x:c r="A15" s="16" t="str">
+        <x:v>Class Challenge</x:v>
+      </x:c>
+      <x:c r="B15" s="16" t="str">
+        <x:v>Constrained client portfolio model with linked calculations, a comparison table, and a recommendation.</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>Only graded tab</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="44" customHeight="1">
-      <x:c r="A16" s="4" t="inlineStr">
+      <x:c r="A16" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">FormulaReferenceCard</x:t>
         </x:is>
       </x:c>
-      <x:c r="B16" s="4" t="inlineStr">
+      <x:c r="B16" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Reference formulas and Excel syntax for stocks, bonds, ROI, and NAV.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" s="4" t="inlineStr">
+      <x:c r="C16" s="16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Reference only</x:t>
         </x:is>
@@ -686,10 +1949,8 @@
       <x:c r="H19" s="15" t="n"/>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I can read a stock quote and calculate bid-ask spread, dividend yield, and P/E interpretation.</x:t>
-        </x:is>
+      <x:c r="A20" s="16" t="str">
+        <x:v>I can read a stock quote and calculate bid-ask spread and dividend yield.</x:v>
       </x:c>
       <x:c r="B20" s="14" t="n"/>
       <x:c r="C20" s="14" t="n"/>
@@ -700,10 +1961,8 @@
       <x:c r="H20" s="15" t="n"/>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I can allocate preferred and common dividends before making an investment recommendation.</x:t>
-        </x:is>
+      <x:c r="A21" s="16" t="str">
+        <x:v>I can calculate ROI while accounting for buy commission, sell commission, and dividends.</x:v>
       </x:c>
       <x:c r="B21" s="14" t="n"/>
       <x:c r="C21" s="14" t="n"/>
@@ -714,10 +1973,8 @@
       <x:c r="H21" s="15" t="n"/>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I can calculate ROI while accounting for buy commission, sell commission, and dividends.</x:t>
-        </x:is>
+      <x:c r="A22" s="16" t="str">
+        <x:v>I can convert a bond quote, calculate current yield, and calculate mutual fund NAV.</x:v>
       </x:c>
       <x:c r="B22" s="14" t="n"/>
       <x:c r="C22" s="14" t="n"/>
@@ -728,10 +1985,8 @@
       <x:c r="H22" s="15" t="n"/>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I can convert bond quotes into dollar prices and calculate current yield.</x:t>
-        </x:is>
+      <x:c r="A23" s="16" t="str">
+        <x:v>I can compare investment alternatives against explicit client constraints.</x:v>
       </x:c>
       <x:c r="B23" s="14" t="n"/>
       <x:c r="C23" s="14" t="n"/>
@@ -742,10 +1997,8 @@
       <x:c r="H23" s="15" t="n"/>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I can calculate mutual fund NAV and use it to price a share purchase.</x:t>
-        </x:is>
+      <x:c r="A24" s="16" t="str">
+        <x:v>I can recommend an eligible investment and explain the evidence behind my choice.</x:v>
       </x:c>
       <x:c r="B24" s="14" t="n"/>
       <x:c r="C24" s="14" t="n"/>
@@ -2067,661 +3320,1112 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="7" customWidth="1"/>
-    <x:col min="2" max="2" width="30" customWidth="1"/>
-    <x:col min="3" max="3" width="58" customWidth="1"/>
-    <x:col min="4" max="4" width="18" customWidth="1"/>
-    <x:col min="5" max="5" width="16" customWidth="1"/>
-    <x:col min="6" max="6" width="18" customWidth="1"/>
-    <x:col min="7" max="7" width="16" customWidth="1"/>
-    <x:col min="8" max="8" width="18" customWidth="1"/>
-    <x:col min="9" max="9" width="16" customWidth="1"/>
-    <x:col min="10" max="10" width="18" customWidth="1"/>
-    <x:col min="11" max="11" width="16" customWidth="1"/>
-    <x:col min="12" max="12" width="18" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="6" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="16" customWidth="1"/>
     <x:col min="14" max="14" width="18" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Class Challenge - Investment Math Desk</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="14" t="n"/>
-      <x:c r="C1" s="14" t="n"/>
-      <x:c r="D1" s="14" t="n"/>
-      <x:c r="E1" s="14" t="n"/>
-      <x:c r="F1" s="14" t="n"/>
-      <x:c r="G1" s="14" t="n"/>
-      <x:c r="H1" s="14" t="n"/>
-      <x:c r="I1" s="14" t="n"/>
-      <x:c r="J1" s="14" t="n"/>
-      <x:c r="K1" s="14" t="n"/>
-      <x:c r="L1" s="14" t="n"/>
-      <x:c r="M1" s="14" t="n"/>
-      <x:c r="N1" s="15" t="n"/>
-    </x:row>
-    <x:row r="2" ht="36" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Read each scenario, extract the needed inputs, and calculate the final numeric answer. Yellow input and final answer cells are blank in the public starter.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="14" t="n"/>
-      <x:c r="C2" s="14" t="n"/>
-      <x:c r="D2" s="14" t="n"/>
-      <x:c r="E2" s="14" t="n"/>
-      <x:c r="F2" s="14" t="n"/>
-      <x:c r="G2" s="14" t="n"/>
-      <x:c r="H2" s="14" t="n"/>
-      <x:c r="I2" s="14" t="n"/>
-      <x:c r="J2" s="14" t="n"/>
-      <x:c r="K2" s="14" t="n"/>
-      <x:c r="L2" s="14" t="n"/>
-      <x:c r="M2" s="14" t="n"/>
-      <x:c r="N2" s="15" t="n"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Q</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Skill</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Scenario</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 1 label</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 2 label</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 2</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 3 label</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 4 label</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 5 label</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Input 5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="N4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Final Answer</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="58" customHeight="1">
-      <x:c r="A5" s="4" t="n">
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="339" t="str">
+        <x:v>Class Challenge - Meridian Client Portfolio Recommendation</x:v>
+      </x:c>
+      <x:c r="B1" s="339"/>
+      <x:c r="C1" s="339"/>
+      <x:c r="D1" s="339"/>
+      <x:c r="E1" s="339"/>
+      <x:c r="F1" s="339"/>
+      <x:c r="G1" s="339"/>
+      <x:c r="H1" s="339"/>
+      <x:c r="I1" s="339"/>
+      <x:c r="J1" s="339"/>
+      <x:c r="K1" s="339"/>
+      <x:c r="L1" s="339"/>
+      <x:c r="M1"/>
+      <x:c r="N1"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="94" t="str">
+        <x:v>Start in class. Finish for homework. Build linked calculations, compare every alternative, test the constraints, and defend one recommendation.</x:v>
+      </x:c>
+      <x:c r="B2" s="94"/>
+      <x:c r="C2" s="94"/>
+      <x:c r="D2" s="94"/>
+      <x:c r="E2" s="94"/>
+      <x:c r="F2" s="94"/>
+      <x:c r="G2" s="94"/>
+      <x:c r="H2" s="94"/>
+      <x:c r="I2" s="94"/>
+      <x:c r="J2" s="94"/>
+      <x:c r="K2" s="94"/>
+      <x:c r="L2" s="94"/>
+      <x:c r="M2"/>
+      <x:c r="N2"/>
+    </x:row>
+    <x:row r="4" ht="26" customHeight="1">
+      <x:c r="A4" s="335" t="str">
+        <x:v>CLIENT BRIEF</x:v>
+      </x:c>
+      <x:c r="B4" s="336"/>
+      <x:c r="C4" s="336"/>
+      <x:c r="D4" s="336"/>
+      <x:c r="E4" s="336"/>
+      <x:c r="F4" s="336"/>
+      <x:c r="G4" s="336"/>
+      <x:c r="H4" s="336"/>
+      <x:c r="I4" s="336"/>
+      <x:c r="J4" s="336"/>
+      <x:c r="K4" s="336"/>
+      <x:c r="L4" s="337"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+    </x:row>
+    <x:row r="5" ht="38" customHeight="1">
+      <x:c r="A5" s="95" t="str">
+        <x:v>Client</x:v>
+      </x:c>
+      <x:c r="B5" s="95" t="str">
+        <x:v>Income-focused client with an $8,000 allocation</x:v>
+      </x:c>
+      <x:c r="C5" s="95" t="str">
+        <x:v>Recommend one investment only after the comparison table proves it meets every client constraint. Use 1 for pass and 0 for fail.</x:v>
+      </x:c>
+      <x:c r="D5" s="95"/>
+      <x:c r="E5" s="95"/>
+      <x:c r="F5" s="95"/>
+      <x:c r="G5" s="95"/>
+      <x:c r="H5" s="95"/>
+      <x:c r="I5" s="95"/>
+      <x:c r="J5" s="95"/>
+      <x:c r="K5" s="95"/>
+      <x:c r="L5" s="95"/>
+      <x:c r="N5"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="311" t="str">
+        <x:v>Constraint</x:v>
+      </x:c>
+      <x:c r="B6" s="311" t="str">
+        <x:v>Threshold</x:v>
+      </x:c>
+      <x:c r="C6" s="311" t="str">
+        <x:v>Lesson-supported interpretation</x:v>
+      </x:c>
+      <x:c r="D6" s="311"/>
+      <x:c r="E6" s="311"/>
+      <x:c r="F6" s="311"/>
+      <x:c r="G6" s="311"/>
+      <x:c r="H6" s="311"/>
+      <x:c r="I6" s="311"/>
+      <x:c r="J6" s="311"/>
+      <x:c r="K6" s="311"/>
+      <x:c r="L6" s="311"/>
+      <x:c r="N6"/>
+    </x:row>
+    <x:row r="7" ht="30" customHeight="1">
+      <x:c r="A7" s="95" t="str">
+        <x:v>Maximum investment cost</x:v>
+      </x:c>
+      <x:c r="B7" s="353" t="n">
+        <x:v>8000</x:v>
+      </x:c>
+      <x:c r="C7" s="95" t="str">
+        <x:v>Cost must fit the allocation.</x:v>
+      </x:c>
+      <x:c r="D7" s="95"/>
+      <x:c r="E7" s="95"/>
+      <x:c r="F7" s="95"/>
+      <x:c r="G7" s="95"/>
+      <x:c r="H7" s="95"/>
+      <x:c r="I7" s="95"/>
+      <x:c r="J7" s="95"/>
+      <x:c r="K7" s="95"/>
+      <x:c r="L7" s="95"/>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+    </x:row>
+    <x:row r="8" ht="30" customHeight="1">
+      <x:c r="A8" s="95" t="str">
+        <x:v>Minimum current income yield</x:v>
+      </x:c>
+      <x:c r="B8" s="354" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="C8" s="95" t="str">
+        <x:v>Pass the performance test with current yield at or above 4.00% OR observed ROI at or above 6.00%.</x:v>
+      </x:c>
+      <x:c r="D8" s="95"/>
+      <x:c r="E8" s="95"/>
+      <x:c r="F8" s="95"/>
+      <x:c r="G8" s="95"/>
+      <x:c r="H8" s="95"/>
+      <x:c r="I8" s="95"/>
+      <x:c r="J8" s="95"/>
+      <x:c r="K8" s="95"/>
+      <x:c r="L8" s="95"/>
+      <x:c r="N8"/>
+    </x:row>
+    <x:row r="9" ht="30" customHeight="1">
+      <x:c r="A9" s="95" t="str">
+        <x:v>Minimum observed ROI</x:v>
+      </x:c>
+      <x:c r="B9" s="354" t="n">
+        <x:v>0.06</x:v>
+      </x:c>
+      <x:c r="C9" s="95" t="str">
+        <x:v>A past ROI is evidence for this scenario, not a promise of future performance.</x:v>
+      </x:c>
+      <x:c r="D9" s="95"/>
+      <x:c r="E9" s="95"/>
+      <x:c r="F9" s="95"/>
+      <x:c r="G9" s="95"/>
+      <x:c r="H9" s="95"/>
+      <x:c r="I9" s="95"/>
+      <x:c r="J9" s="95"/>
+      <x:c r="K9" s="95"/>
+      <x:c r="L9" s="95"/>
+      <x:c r="N9"/>
+    </x:row>
+    <x:row r="10" ht="30" customHeight="1">
+      <x:c r="A10" s="95" t="str">
+        <x:v>Required lower-risk proxy flag</x:v>
+      </x:c>
+      <x:c r="B10" s="340" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bid-ask spread</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meridian reviews a stock quote showing a current price of $52.40, bid of $52.33, and ask of $52.47. Calculate the bid-ask spread.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bid</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="6" t="n"/>
-      <x:c r="F5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ask</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="6" t="n"/>
-      <x:c r="N5" s="6" t="n"/>
-    </x:row>
-    <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dividend yield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MAGH trades at $39.62 and pays an annual dividend of $1.21 per share. Calculate the dividend yield.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stock price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="6" t="n"/>
-      <x:c r="F6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual dividend</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="6" t="n"/>
-      <x:c r="N6" s="12" t="n"/>
-    </x:row>
-    <x:row r="7" ht="58" customHeight="1">
-      <x:c r="A7" s="4" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Common dividend per share</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A company declares $10,000 in dividends. Preferred stock is 8% with $50 par value and 1,000 preferred shares. There are 4,000 common shares. Calculate the dividend per common share.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total dividends</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="9" t="n"/>
-      <x:c r="F7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Preferred rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G7" s="10" t="n"/>
-      <x:c r="H7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Par value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" s="9" t="n"/>
-      <x:c r="J7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Preferred shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K7" s="11" t="n"/>
-      <x:c r="L7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Common shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M7" s="11" t="n"/>
-      <x:c r="N7" s="6" t="n"/>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
-      <x:c r="A8" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total preferred dividend</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Preferred shareholders receive 8% on $50 par value, with 1,000 preferred shares outstanding. Calculate the total preferred dividend.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Preferred rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="10" t="n"/>
-      <x:c r="F8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Par value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="9" t="n"/>
-      <x:c r="H8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Preferred shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" s="11" t="n"/>
-      <x:c r="N8" s="9" t="n"/>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
-      <x:c r="A9" s="4" t="n">
+      <x:c r="C10" s="95" t="str">
+        <x:v>1 only for creditor priority (bond) or diversified pooled ownership (mutual fund); 0 for an individual stock.</x:v>
+      </x:c>
+      <x:c r="D10" s="95"/>
+      <x:c r="E10" s="95"/>
+      <x:c r="F10" s="95"/>
+      <x:c r="G10" s="95"/>
+      <x:c r="H10" s="95"/>
+      <x:c r="I10" s="95"/>
+      <x:c r="J10" s="95"/>
+      <x:c r="K10" s="95"/>
+      <x:c r="L10" s="95"/>
+      <x:c r="N10"/>
+    </x:row>
+    <x:row r="11" ht="58" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11"/>
+      <x:c r="N11"/>
+    </x:row>
+    <x:row r="12" ht="58" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12"/>
+      <x:c r="C12"/>
+      <x:c r="D12"/>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="N12"/>
+    </x:row>
+    <x:row r="13" ht="26" customHeight="1">
+      <x:c r="A13" s="335" t="str">
+        <x:v>ALTERNATIVE 1 - MAGH COMMON STOCK</x:v>
+      </x:c>
+      <x:c r="B13" s="336"/>
+      <x:c r="C13" s="336"/>
+      <x:c r="D13" s="336"/>
+      <x:c r="E13" s="336"/>
+      <x:c r="F13" s="336"/>
+      <x:c r="G13" s="336"/>
+      <x:c r="H13" s="336"/>
+      <x:c r="I13" s="336"/>
+      <x:c r="J13" s="336"/>
+      <x:c r="K13" s="336"/>
+      <x:c r="L13" s="337"/>
+      <x:c r="N13"/>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="311" t="str">
+        <x:v>Stock quote / return inputs</x:v>
+      </x:c>
+      <x:c r="B14" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C14" s="95"/>
+      <x:c r="D14" s="311" t="str">
+        <x:v>Transaction inputs</x:v>
+      </x:c>
+      <x:c r="E14" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="F14" s="95"/>
+      <x:c r="G14" s="311" t="str">
+        <x:v>Linked calculation</x:v>
+      </x:c>
+      <x:c r="H14" s="311" t="str">
+        <x:v>Formula result</x:v>
+      </x:c>
+      <x:c r="I14" s="95"/>
+      <x:c r="J14" s="311" t="str">
+        <x:v>Product classification</x:v>
+      </x:c>
+      <x:c r="K14" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="N14"/>
+    </x:row>
+    <x:row r="15" ht="26" customHeight="1">
+      <x:c r="A15" s="95" t="str">
+        <x:v>Bid price</x:v>
+      </x:c>
+      <x:c r="B15" s="355" t="n">
+        <x:v>39.55</x:v>
+      </x:c>
+      <x:c r="C15" s="95"/>
+      <x:c r="D15" s="95" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="E15" s="340" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="F15" s="95"/>
+      <x:c r="G15" s="95" t="str">
+        <x:v>Bid-ask spread</x:v>
+      </x:c>
+      <x:c r="H15" s="356"/>
+      <x:c r="I15" s="95"/>
+      <x:c r="J15" s="95" t="str">
+        <x:v>Product type</x:v>
+      </x:c>
+      <x:c r="K15" s="340" t="str">
+        <x:v>Individual common stock</x:v>
+      </x:c>
+      <x:c r="N15"/>
+    </x:row>
+    <x:row r="16" ht="26" customHeight="1">
+      <x:c r="A16" s="95" t="str">
+        <x:v>Ask price</x:v>
+      </x:c>
+      <x:c r="B16" s="355" t="n">
+        <x:v>39.68</x:v>
+      </x:c>
+      <x:c r="C16" s="95"/>
+      <x:c r="D16" s="95" t="str">
+        <x:v>Buy price/share</x:v>
+      </x:c>
+      <x:c r="E16" s="355" t="n">
+        <x:v>39.09</x:v>
+      </x:c>
+      <x:c r="F16" s="95"/>
+      <x:c r="G16" s="95" t="str">
+        <x:v>Dividend yield</x:v>
+      </x:c>
+      <x:c r="H16" s="358"/>
+      <x:c r="I16" s="95"/>
+      <x:c r="J16" s="95"/>
+      <x:c r="K16" s="95"/>
+      <x:c r="N16"/>
+    </x:row>
+    <x:row r="17" ht="26" customHeight="1">
+      <x:c r="A17" s="95" t="str">
+        <x:v>Last price</x:v>
+      </x:c>
+      <x:c r="B17" s="355" t="n">
+        <x:v>39.62</x:v>
+      </x:c>
+      <x:c r="C17" s="95"/>
+      <x:c r="D17" s="95" t="str">
+        <x:v>Sale price/share</x:v>
+      </x:c>
+      <x:c r="E17" s="355" t="n">
+        <x:v>41.1</x:v>
+      </x:c>
+      <x:c r="F17" s="95"/>
+      <x:c r="G17" s="95" t="str">
+        <x:v>Total buy cost</x:v>
+      </x:c>
+      <x:c r="H17" s="356"/>
+      <x:c r="I17" s="95"/>
+      <x:c r="J17" s="95"/>
+      <x:c r="K17" s="95"/>
+      <x:c r="N17"/>
+    </x:row>
+    <x:row r="18" ht="26" customHeight="1">
+      <x:c r="A18" s="95" t="str">
+        <x:v>Annual dividend/share</x:v>
+      </x:c>
+      <x:c r="B18" s="355" t="n">
+        <x:v>1.21</x:v>
+      </x:c>
+      <x:c r="C18" s="95"/>
+      <x:c r="D18" s="95" t="str">
+        <x:v>Commission rate</x:v>
+      </x:c>
+      <x:c r="E18" s="354" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="F18" s="95"/>
+      <x:c r="G18" s="95" t="str">
+        <x:v>Net sale proceeds</x:v>
+      </x:c>
+      <x:c r="H18" s="356"/>
+      <x:c r="I18" s="95"/>
+      <x:c r="J18" s="95"/>
+      <x:c r="K18" s="95"/>
+      <x:c r="N18"/>
+    </x:row>
+    <x:row r="19" ht="26" customHeight="1">
+      <x:c r="A19" s="95"/>
+      <x:c r="B19" s="95"/>
+      <x:c r="C19" s="95"/>
+      <x:c r="D19" s="95"/>
+      <x:c r="E19" s="95"/>
+      <x:c r="F19" s="95"/>
+      <x:c r="G19" s="95" t="str">
+        <x:v>Total dividends</x:v>
+      </x:c>
+      <x:c r="H19" s="356"/>
+      <x:c r="I19" s="95"/>
+      <x:c r="J19" s="95"/>
+      <x:c r="K19" s="95"/>
+      <x:c r="N19"/>
+    </x:row>
+    <x:row r="20" ht="26" customHeight="1">
+      <x:c r="A20" s="95"/>
+      <x:c r="B20" s="95"/>
+      <x:c r="C20" s="95"/>
+      <x:c r="D20" s="95"/>
+      <x:c r="E20" s="95"/>
+      <x:c r="F20" s="95"/>
+      <x:c r="G20" s="95" t="str">
+        <x:v>Observed ROI</x:v>
+      </x:c>
+      <x:c r="H20" s="358"/>
+      <x:c r="I20" s="95"/>
+      <x:c r="J20" s="95"/>
+      <x:c r="K20" s="95"/>
+    </x:row>
+    <x:row r="21" ht="26" customHeight="1">
+      <x:c r="A21" s="95"/>
+      <x:c r="B21" s="95"/>
+      <x:c r="C21" s="95"/>
+      <x:c r="D21" s="95"/>
+      <x:c r="E21" s="95"/>
+      <x:c r="F21" s="95"/>
+      <x:c r="G21" s="95" t="str">
+        <x:v>Lower-risk proxy flag</x:v>
+      </x:c>
+      <x:c r="H21" s="361"/>
+      <x:c r="I21" s="95"/>
+      <x:c r="J21" s="95"/>
+      <x:c r="K21" s="95"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="95"/>
+      <x:c r="B22" s="95"/>
+      <x:c r="C22" s="95"/>
+      <x:c r="D22" s="95"/>
+      <x:c r="E22" s="95"/>
+      <x:c r="F22" s="95"/>
+      <x:c r="G22" s="95"/>
+      <x:c r="H22" s="95"/>
+      <x:c r="I22" s="95"/>
+      <x:c r="J22" s="95"/>
+      <x:c r="K22" s="95"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="95"/>
+      <x:c r="B23" s="95"/>
+      <x:c r="C23" s="95"/>
+      <x:c r="D23" s="95"/>
+      <x:c r="E23" s="95"/>
+      <x:c r="F23" s="95"/>
+      <x:c r="G23" s="95"/>
+      <x:c r="H23" s="95"/>
+      <x:c r="I23" s="95"/>
+      <x:c r="J23" s="95"/>
+      <x:c r="K23" s="95"/>
+    </x:row>
+    <x:row r="24" ht="26" customHeight="1">
+      <x:c r="A24" s="342" t="str">
+        <x:v>ALTERNATIVE 2 - MERIDIAN 4% CORPORATE BOND</x:v>
+      </x:c>
+      <x:c r="B24" s="343"/>
+      <x:c r="C24" s="343"/>
+      <x:c r="D24" s="343"/>
+      <x:c r="E24" s="343"/>
+      <x:c r="F24" s="343"/>
+      <x:c r="G24" s="343"/>
+      <x:c r="H24" s="343"/>
+      <x:c r="I24" s="343"/>
+      <x:c r="J24" s="343"/>
+      <x:c r="K24" s="343"/>
+      <x:c r="L24" s="337"/>
+    </x:row>
+    <x:row r="25" ht="30" customHeight="1">
+      <x:c r="A25" s="311" t="str">
+        <x:v>Bond inputs</x:v>
+      </x:c>
+      <x:c r="B25" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C25" s="95"/>
+      <x:c r="D25" s="95"/>
+      <x:c r="E25" s="95"/>
+      <x:c r="F25" s="95"/>
+      <x:c r="G25" s="311" t="str">
+        <x:v>Linked calculation</x:v>
+      </x:c>
+      <x:c r="H25" s="311" t="str">
+        <x:v>Formula result</x:v>
+      </x:c>
+      <x:c r="I25" s="95"/>
+      <x:c r="J25" s="311" t="str">
+        <x:v>Product classification</x:v>
+      </x:c>
+      <x:c r="K25" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="95" t="str">
+        <x:v>Quoted price</x:v>
+      </x:c>
+      <x:c r="B26" s="355" t="n">
+        <x:v>99.59</x:v>
+      </x:c>
+      <x:c r="C26" s="95"/>
+      <x:c r="D26" s="95"/>
+      <x:c r="E26" s="95"/>
+      <x:c r="F26" s="95"/>
+      <x:c r="G26" s="95" t="str">
+        <x:v>Dollar price per bond</x:v>
+      </x:c>
+      <x:c r="H26" s="356"/>
+      <x:c r="I26" s="95"/>
+      <x:c r="J26" s="95" t="str">
+        <x:v>Product type</x:v>
+      </x:c>
+      <x:c r="K26" s="340" t="str">
+        <x:v>Bond</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="95" t="str">
+        <x:v>Face value</x:v>
+      </x:c>
+      <x:c r="B27" s="355" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C27" s="95"/>
+      <x:c r="D27" s="95"/>
+      <x:c r="E27" s="95"/>
+      <x:c r="F27" s="95"/>
+      <x:c r="G27" s="95" t="str">
+        <x:v>Total purchase cost</x:v>
+      </x:c>
+      <x:c r="H27" s="356"/>
+      <x:c r="I27" s="95"/>
+      <x:c r="J27" s="95"/>
+      <x:c r="K27" s="95"/>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="95" t="str">
+        <x:v>Stated interest rate</x:v>
+      </x:c>
+      <x:c r="B28" s="354" t="n">
+        <x:v>0.04</x:v>
+      </x:c>
+      <x:c r="C28" s="95"/>
+      <x:c r="D28" s="95"/>
+      <x:c r="E28" s="95"/>
+      <x:c r="F28" s="95"/>
+      <x:c r="G28" s="95" t="str">
+        <x:v>Annual interest/bond</x:v>
+      </x:c>
+      <x:c r="H28" s="356"/>
+      <x:c r="I28" s="95"/>
+      <x:c r="J28" s="95"/>
+      <x:c r="K28" s="95"/>
+    </x:row>
+    <x:row r="29" ht="26" customHeight="1">
+      <x:c r="A29" s="95" t="str">
+        <x:v>Number of bonds</x:v>
+      </x:c>
+      <x:c r="B29" s="340" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total buy cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A Meridian analyst buys 200 shares at $39.09 per share and pays a 1% buy commission. Calculate total buy cost including commission.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="11" t="n"/>
-      <x:c r="F9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Buy price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G9" s="6" t="n"/>
-      <x:c r="H9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Commission rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" s="10" t="n"/>
-      <x:c r="N9" s="6" t="n"/>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
-      <x:c r="A10" s="4" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Net sale proceeds</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">The analyst sells 200 shares at $41.10 per share and pays a 1% sell commission. Calculate net sale proceeds after commission.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="11" t="n"/>
-      <x:c r="F10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sale price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G10" s="6" t="n"/>
-      <x:c r="H10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Commission rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" s="10" t="n"/>
-      <x:c r="N10" s="6" t="n"/>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
-      <x:c r="A11" s="4" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROI with commissions and dividends</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">An analyst bought 200 shares at $39.09, sold them at $41.10 one year later, paid a 1% commission on both transactions, and received $1.21 per share in annual dividends. Calculate ROI.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="11" t="n"/>
-      <x:c r="F11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Buy price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G11" s="6" t="n"/>
-      <x:c r="H11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sale price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" s="6" t="n"/>
-      <x:c r="J11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Commission rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K11" s="10" t="n"/>
-      <x:c r="L11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dividend/share</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M11" s="6" t="n"/>
-      <x:c r="N11" s="12" t="n"/>
-    </x:row>
-    <x:row r="12" ht="58" customHeight="1">
-      <x:c r="A12" s="4" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bond dollar price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A bond is quoted at 103.75 and has a $1,000 face value. Calculate the dollar price per bond.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quoted price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="13" t="n"/>
-      <x:c r="F12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Face value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="9" t="n"/>
-      <x:c r="N12" s="6" t="n"/>
-    </x:row>
-    <x:row r="13" ht="58" customHeight="1">
-      <x:c r="A13" s="4" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Premium amount</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bond A is quoted at 105.25 and has a $1,000 face value. Calculate the dollar amount above par.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quoted price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="13" t="n"/>
-      <x:c r="F13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Face value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G13" s="9" t="n"/>
-      <x:c r="N13" s="6" t="n"/>
-    </x:row>
-    <x:row r="14" ht="58" customHeight="1">
-      <x:c r="A14" s="4" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Current yield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A 5% bond is quoted at 97.50 and has a $1,000 face value. Calculate the current yield.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stated rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="10" t="n"/>
-      <x:c r="F14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quoted price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G14" s="13" t="n"/>
-      <x:c r="H14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Face value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" s="9" t="n"/>
-      <x:c r="N14" s="12" t="n"/>
-    </x:row>
-    <x:row r="15" ht="58" customHeight="1">
-      <x:c r="A15" s="4" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total purchase cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meridian purchases 5 bonds at a quoted price of 99.59. Each bond has a $1,000 face value. Calculate total purchase cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quoted price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="13" t="n"/>
-      <x:c r="F15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Face value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G15" s="9" t="n"/>
-      <x:c r="H15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Number of bonds</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" s="11" t="n"/>
-      <x:c r="N15" s="6" t="n"/>
-    </x:row>
-    <x:row r="16" ht="58" customHeight="1">
-      <x:c r="A16" s="4" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total annual interest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meridian holds 5 bonds with a 4% stated interest rate and $1,000 par value. Calculate total annual interest received.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Stated rate</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" s="10" t="n"/>
-      <x:c r="F16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Face value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G16" s="9" t="n"/>
-      <x:c r="H16" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Number of bonds</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" s="11" t="n"/>
-      <x:c r="N16" s="6" t="n"/>
-    </x:row>
-    <x:row r="17" ht="58" customHeight="1">
-      <x:c r="A17" s="4" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mutual fund NAV</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meridian's Balanced Fund has $8,400,000 in holdings, $950,000 in liabilities, and 1,200,000 shares outstanding. Calculate NAV per share.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Holdings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="9" t="n"/>
-      <x:c r="F17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Liabilities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G17" s="9" t="n"/>
-      <x:c r="H17" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" s="11" t="n"/>
-      <x:c r="N17" s="6" t="n"/>
-    </x:row>
-    <x:row r="18" ht="58" customHeight="1">
-      <x:c r="A18" s="4" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fund purchase cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">An investor wants to buy 100 shares of Meridian's Balanced Fund. The fund has $8,400,000 in holdings, $950,000 in liabilities, and 1,200,000 shares outstanding. Use rounded NAV per share to calculate total purchase cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Holdings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" s="9" t="n"/>
-      <x:c r="F18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Liabilities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G18" s="9" t="n"/>
-      <x:c r="H18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" s="11" t="n"/>
-      <x:c r="J18" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Purchase shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="11" t="n"/>
-      <x:c r="N18" s="6" t="n"/>
-    </x:row>
-    <x:row r="19" ht="58" customHeight="1">
-      <x:c r="A19" s="4" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Growth &amp; Income Fund purchase cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Meridian Growth &amp; Income Fund has $5,550,000 in holdings, $770,000 in liabilities, and 600,000 shares outstanding. A client wants to buy 80 shares. Use rounded NAV per share to calculate purchase cost.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Holdings</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" s="9" t="n"/>
-      <x:c r="F19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Liabilities</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G19" s="9" t="n"/>
-      <x:c r="H19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" s="11" t="n"/>
-      <x:c r="J19" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Purchase shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="11" t="n"/>
-      <x:c r="N19" s="6" t="n"/>
+      <x:c r="C29" s="95"/>
+      <x:c r="D29" s="95"/>
+      <x:c r="E29" s="95"/>
+      <x:c r="F29" s="95"/>
+      <x:c r="G29" s="95" t="str">
+        <x:v>Total annual income</x:v>
+      </x:c>
+      <x:c r="H29" s="356"/>
+      <x:c r="I29" s="95"/>
+      <x:c r="J29" s="95"/>
+      <x:c r="K29" s="95"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="95"/>
+      <x:c r="B30" s="95"/>
+      <x:c r="C30" s="95"/>
+      <x:c r="D30" s="95"/>
+      <x:c r="E30" s="95"/>
+      <x:c r="F30" s="95"/>
+      <x:c r="G30" s="95" t="str">
+        <x:v>Current yield</x:v>
+      </x:c>
+      <x:c r="H30" s="358"/>
+      <x:c r="I30" s="95"/>
+      <x:c r="J30" s="95"/>
+      <x:c r="K30" s="95"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="95"/>
+      <x:c r="B31" s="95"/>
+      <x:c r="C31" s="95"/>
+      <x:c r="D31" s="95"/>
+      <x:c r="E31" s="95"/>
+      <x:c r="F31" s="95"/>
+      <x:c r="G31" s="95" t="str">
+        <x:v>Lower-risk proxy flag</x:v>
+      </x:c>
+      <x:c r="H31" s="361"/>
+      <x:c r="I31" s="95"/>
+      <x:c r="J31" s="95"/>
+      <x:c r="K31" s="95"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="95"/>
+      <x:c r="B32" s="95"/>
+      <x:c r="C32" s="95"/>
+      <x:c r="D32" s="95"/>
+      <x:c r="E32" s="95"/>
+      <x:c r="F32" s="95"/>
+      <x:c r="G32" s="95"/>
+      <x:c r="H32" s="95"/>
+      <x:c r="I32" s="95"/>
+      <x:c r="J32" s="95"/>
+      <x:c r="K32" s="95"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="95"/>
+      <x:c r="B33" s="95"/>
+      <x:c r="C33" s="95"/>
+      <x:c r="D33" s="95"/>
+      <x:c r="E33" s="95"/>
+      <x:c r="F33" s="95"/>
+      <x:c r="G33" s="95"/>
+      <x:c r="H33" s="95"/>
+      <x:c r="I33" s="95"/>
+      <x:c r="J33" s="95"/>
+      <x:c r="K33" s="95"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="95"/>
+      <x:c r="B34" s="95"/>
+      <x:c r="C34" s="95"/>
+      <x:c r="D34" s="95"/>
+      <x:c r="E34" s="95"/>
+      <x:c r="F34" s="95"/>
+      <x:c r="G34" s="95"/>
+      <x:c r="H34" s="95"/>
+      <x:c r="I34" s="95"/>
+      <x:c r="J34" s="95"/>
+      <x:c r="K34" s="95"/>
+    </x:row>
+    <x:row r="35" ht="26" customHeight="1">
+      <x:c r="A35" s="342" t="str">
+        <x:v>ALTERNATIVE 3 - MERIDIAN BALANCED FUND</x:v>
+      </x:c>
+      <x:c r="B35" s="343"/>
+      <x:c r="C35" s="343"/>
+      <x:c r="D35" s="343"/>
+      <x:c r="E35" s="343"/>
+      <x:c r="F35" s="343"/>
+      <x:c r="G35" s="343"/>
+      <x:c r="H35" s="343"/>
+      <x:c r="I35" s="343"/>
+      <x:c r="J35" s="343"/>
+      <x:c r="K35" s="343"/>
+      <x:c r="L35" s="337"/>
+    </x:row>
+    <x:row r="36" ht="30" customHeight="1">
+      <x:c r="A36" s="311" t="str">
+        <x:v>Fund valuation inputs</x:v>
+      </x:c>
+      <x:c r="B36" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C36" s="95"/>
+      <x:c r="D36" s="95"/>
+      <x:c r="E36" s="95"/>
+      <x:c r="F36" s="95"/>
+      <x:c r="G36" s="311" t="str">
+        <x:v>Linked calculation</x:v>
+      </x:c>
+      <x:c r="H36" s="311" t="str">
+        <x:v>Formula result</x:v>
+      </x:c>
+      <x:c r="I36" s="95"/>
+      <x:c r="J36" s="311" t="str">
+        <x:v>Product classification</x:v>
+      </x:c>
+      <x:c r="K36" s="311" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="26" customHeight="1">
+      <x:c r="A37" s="95" t="str">
+        <x:v>Holdings</x:v>
+      </x:c>
+      <x:c r="B37" s="355" t="n">
+        <x:v>8400000</x:v>
+      </x:c>
+      <x:c r="C37" s="95"/>
+      <x:c r="D37" s="95"/>
+      <x:c r="E37" s="95"/>
+      <x:c r="F37" s="95"/>
+      <x:c r="G37" s="95" t="str">
+        <x:v>Net assets</x:v>
+      </x:c>
+      <x:c r="H37" s="356"/>
+      <x:c r="I37" s="95"/>
+      <x:c r="J37" s="95" t="str">
+        <x:v>Product type</x:v>
+      </x:c>
+      <x:c r="K37" s="340" t="str">
+        <x:v>Diversified mutual fund</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="26" customHeight="1">
+      <x:c r="A38" s="95" t="str">
+        <x:v>Liabilities</x:v>
+      </x:c>
+      <x:c r="B38" s="355" t="n">
+        <x:v>950000</x:v>
+      </x:c>
+      <x:c r="C38" s="95"/>
+      <x:c r="D38" s="95"/>
+      <x:c r="E38" s="95"/>
+      <x:c r="F38" s="95"/>
+      <x:c r="G38" s="95" t="str">
+        <x:v>NAV per share</x:v>
+      </x:c>
+      <x:c r="H38" s="356"/>
+      <x:c r="I38" s="95"/>
+      <x:c r="J38" s="95"/>
+      <x:c r="K38" s="95"/>
+    </x:row>
+    <x:row r="39" ht="26" customHeight="1">
+      <x:c r="A39" s="95" t="str">
+        <x:v>Shares outstanding</x:v>
+      </x:c>
+      <x:c r="B39" s="340" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="C39" s="95"/>
+      <x:c r="D39" s="95"/>
+      <x:c r="E39" s="95"/>
+      <x:c r="F39" s="95"/>
+      <x:c r="G39" s="95" t="str">
+        <x:v>Purchase cost</x:v>
+      </x:c>
+      <x:c r="H39" s="356"/>
+      <x:c r="I39" s="95"/>
+      <x:c r="J39" s="95"/>
+      <x:c r="K39" s="95"/>
+    </x:row>
+    <x:row r="40" ht="26" customHeight="1">
+      <x:c r="A40" s="95" t="str">
+        <x:v>Shares to buy</x:v>
+      </x:c>
+      <x:c r="B40" s="340" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C40" s="95"/>
+      <x:c r="D40" s="95"/>
+      <x:c r="E40" s="95"/>
+      <x:c r="F40" s="95"/>
+      <x:c r="G40" s="95" t="str">
+        <x:v>Current yield / ROI</x:v>
+      </x:c>
+      <x:c r="H40" s="344"/>
+      <x:c r="I40" s="95" t="str">
+        <x:v>Not calculable from the provided M10 fund inputs; do not invent a return.</x:v>
+      </x:c>
+      <x:c r="J40" s="95"/>
+      <x:c r="K40" s="95"/>
+    </x:row>
+    <x:row r="41" ht="26" customHeight="1">
+      <x:c r="A41" s="95"/>
+      <x:c r="B41" s="95"/>
+      <x:c r="C41" s="95"/>
+      <x:c r="D41" s="95"/>
+      <x:c r="E41" s="95"/>
+      <x:c r="F41" s="95"/>
+      <x:c r="G41" s="95" t="str">
+        <x:v>Lower-risk proxy flag</x:v>
+      </x:c>
+      <x:c r="H41" s="361"/>
+      <x:c r="I41" s="95"/>
+      <x:c r="J41" s="95"/>
+      <x:c r="K41" s="95"/>
+    </x:row>
+    <x:row r="46" ht="26" customHeight="1">
+      <x:c r="A46" s="335" t="str">
+        <x:v>COMPARISON TABLE - LINK EVERY METRIC FROM THE CALCULATION BLOCKS</x:v>
+      </x:c>
+      <x:c r="B46" s="336"/>
+      <x:c r="C46" s="336"/>
+      <x:c r="D46" s="336"/>
+      <x:c r="E46" s="336"/>
+      <x:c r="F46" s="336"/>
+      <x:c r="G46" s="336"/>
+      <x:c r="H46" s="336"/>
+      <x:c r="I46" s="336"/>
+      <x:c r="J46" s="336"/>
+      <x:c r="K46" s="336"/>
+      <x:c r="L46" s="337"/>
+    </x:row>
+    <x:row r="47" ht="46" customHeight="1">
+      <x:c r="A47" s="311" t="str">
+        <x:v>Alternative</x:v>
+      </x:c>
+      <x:c r="B47" s="311" t="str">
+        <x:v>Cost</x:v>
+      </x:c>
+      <x:c r="C47" s="311" t="str">
+        <x:v>Income yield</x:v>
+      </x:c>
+      <x:c r="D47" s="311" t="str">
+        <x:v>Observed ROI</x:v>
+      </x:c>
+      <x:c r="E47" s="311" t="str">
+        <x:v>Quote / valuation metric</x:v>
+      </x:c>
+      <x:c r="F47" s="311" t="str">
+        <x:v>Risk proxy</x:v>
+      </x:c>
+      <x:c r="G47" s="311" t="str">
+        <x:v>Budget pass</x:v>
+      </x:c>
+      <x:c r="H47" s="311" t="str">
+        <x:v>Income or return pass</x:v>
+      </x:c>
+      <x:c r="I47" s="311" t="str">
+        <x:v>Risk pass</x:v>
+      </x:c>
+      <x:c r="J47" s="311" t="str">
+        <x:v>Eligible</x:v>
+      </x:c>
+      <x:c r="K47" s="311" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="102"/>
+      <x:c r="B48" s="102"/>
+      <x:c r="C48" s="102"/>
+      <x:c r="D48" s="102"/>
+      <x:c r="E48" s="102"/>
+      <x:c r="F48" s="102"/>
+      <x:c r="G48" s="102"/>
+      <x:c r="H48" s="102"/>
+      <x:c r="I48" s="102"/>
+      <x:c r="J48" s="102"/>
+      <x:c r="K48" s="102"/>
+    </x:row>
+    <x:row r="49" ht="26" customHeight="1">
+      <x:c r="A49" s="102" t="str">
+        <x:v>MAGH Common Stock</x:v>
+      </x:c>
+      <x:c r="B49" s="357"/>
+      <x:c r="C49" s="359"/>
+      <x:c r="D49" s="359"/>
+      <x:c r="E49" s="357"/>
+      <x:c r="F49" s="362"/>
+      <x:c r="G49" s="362"/>
+      <x:c r="H49" s="362"/>
+      <x:c r="I49" s="362"/>
+      <x:c r="J49" s="362"/>
+      <x:c r="K49" s="350" t="str">
+        <x:f>IF(COUNT(G49:J49)&lt;4,"Build tests",IF(J49=1,"Eligible","Not eligible"))</x:f>
+        <x:v>Build tests</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="26" customHeight="1">
+      <x:c r="A50" s="102" t="str">
+        <x:v>Meridian 4% Bond</x:v>
+      </x:c>
+      <x:c r="B50" s="357"/>
+      <x:c r="C50" s="360"/>
+      <x:c r="D50" s="360"/>
+      <x:c r="E50" s="357"/>
+      <x:c r="F50" s="362"/>
+      <x:c r="G50" s="362"/>
+      <x:c r="H50" s="362"/>
+      <x:c r="I50" s="362"/>
+      <x:c r="J50" s="362"/>
+      <x:c r="K50" s="350" t="str">
+        <x:f>IF(COUNT(G50:J50)&lt;4,"Build tests",IF(J50=1,"Eligible","Not eligible"))</x:f>
+        <x:v>Build tests</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="26" customHeight="1">
+      <x:c r="A51" s="102" t="str">
+        <x:v>Meridian Balanced Fund</x:v>
+      </x:c>
+      <x:c r="B51" s="357"/>
+      <x:c r="C51" s="360"/>
+      <x:c r="D51" s="360"/>
+      <x:c r="E51" s="357"/>
+      <x:c r="F51" s="362"/>
+      <x:c r="G51" s="362"/>
+      <x:c r="H51" s="362"/>
+      <x:c r="I51" s="362"/>
+      <x:c r="J51" s="362"/>
+      <x:c r="K51" s="350" t="str">
+        <x:f>IF(COUNT(G51:J51)&lt;4,"Build tests",IF(J51=1,"Eligible","Not eligible"))</x:f>
+        <x:v>Build tests</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="102"/>
+      <x:c r="B52" s="102"/>
+      <x:c r="C52" s="102"/>
+      <x:c r="D52" s="102"/>
+      <x:c r="E52" s="102"/>
+      <x:c r="F52" s="102"/>
+      <x:c r="G52" s="102"/>
+      <x:c r="H52" s="102"/>
+      <x:c r="I52" s="102"/>
+      <x:c r="J52" s="102"/>
+      <x:c r="K52" s="102"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="102" t="str">
+        <x:v>Eligible alternatives</x:v>
+      </x:c>
+      <x:c r="B53" s="363" t="n">
+        <x:f>SUM(J49:J51)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C53" s="102"/>
+      <x:c r="D53" s="102"/>
+      <x:c r="E53" s="102"/>
+      <x:c r="F53" s="102"/>
+      <x:c r="G53" s="102"/>
+      <x:c r="H53" s="102"/>
+      <x:c r="I53" s="102"/>
+      <x:c r="J53" s="102"/>
+      <x:c r="K53" s="102"/>
+    </x:row>
+    <x:row r="55" ht="26" customHeight="1">
+      <x:c r="A55" s="335" t="str">
+        <x:v>RECOMMENDATION</x:v>
+      </x:c>
+      <x:c r="B55" s="336"/>
+      <x:c r="C55" s="336"/>
+      <x:c r="D55" s="336"/>
+      <x:c r="E55" s="336"/>
+      <x:c r="F55" s="336"/>
+      <x:c r="G55" s="336"/>
+      <x:c r="H55" s="336"/>
+      <x:c r="I55" s="336"/>
+      <x:c r="J55" s="336"/>
+      <x:c r="K55" s="336"/>
+      <x:c r="L55" s="337"/>
+    </x:row>
+    <x:row r="56" ht="26" customHeight="1">
+      <x:c r="A56" s="102" t="str">
+        <x:v>Selected recommendation</x:v>
+      </x:c>
+      <x:c r="B56" s="346"/>
+      <x:c r="C56" s="102"/>
+      <x:c r="D56" s="102"/>
+      <x:c r="E56" s="102"/>
+      <x:c r="F56" s="102"/>
+      <x:c r="G56" s="102"/>
+      <x:c r="H56" s="102"/>
+      <x:c r="I56" s="102"/>
+      <x:c r="J56" s="102"/>
+      <x:c r="K56" s="102"/>
+      <x:c r="L56" s="102"/>
+    </x:row>
+    <x:row r="57" ht="26" customHeight="1">
+      <x:c r="A57" s="102" t="str">
+        <x:v>Selected recommendation eligible?</x:v>
+      </x:c>
+      <x:c r="B57" s="363" t="str">
+        <x:f>IF(B56="","",IF(B56=A49,J49,IF(B56=A50,J50,IF(B56=A51,J51,0))))</x:f>
+      </x:c>
+      <x:c r="C57" s="102"/>
+      <x:c r="D57" s="102"/>
+      <x:c r="E57" s="102"/>
+      <x:c r="F57" s="102"/>
+      <x:c r="G57" s="102"/>
+      <x:c r="H57" s="102"/>
+      <x:c r="I57" s="102"/>
+      <x:c r="J57" s="102"/>
+      <x:c r="K57" s="102"/>
+      <x:c r="L57" s="102"/>
+    </x:row>
+    <x:row r="58" ht="26" customHeight="1">
+      <x:c r="A58" s="102" t="str">
+        <x:v>Decision check</x:v>
+      </x:c>
+      <x:c r="B58" s="352" t="str">
+        <x:f>IF(B56="","Choose an alternative",IF(B57=1,"Consistent with calculated constraints","Revise: the selection fails at least one client constraint"))</x:f>
+        <x:v>Choose an alternative</x:v>
+      </x:c>
+      <x:c r="C58" s="102"/>
+      <x:c r="D58" s="102"/>
+      <x:c r="E58" s="102"/>
+      <x:c r="F58" s="102"/>
+      <x:c r="G58" s="102"/>
+      <x:c r="H58" s="102"/>
+      <x:c r="I58" s="102"/>
+      <x:c r="J58" s="102"/>
+      <x:c r="K58" s="102"/>
+      <x:c r="L58" s="102"/>
+    </x:row>
+    <x:row r="60" ht="34" customHeight="1">
+      <x:c r="A60" s="53" t="str">
+        <x:v>Recommendation explanation</x:v>
+      </x:c>
+      <x:c r="B60" s="107" t="str">
+        <x:v>In 2-4 sentences, cite the selected alternative's calculated cost, yield or ROI evidence, and lower-risk proxy. Explain why the other choices fail.</x:v>
+      </x:c>
+      <x:c r="C60" s="107"/>
+      <x:c r="D60" s="107"/>
+      <x:c r="E60" s="107"/>
+      <x:c r="F60" s="107"/>
+      <x:c r="G60" s="107"/>
+      <x:c r="H60" s="107"/>
+      <x:c r="I60" s="107"/>
+      <x:c r="J60" s="107"/>
+      <x:c r="K60" s="107"/>
+      <x:c r="L60" s="51"/>
+    </x:row>
+    <x:row r="61" ht="28" customHeight="1">
+      <x:c r="A61" s="348"/>
+      <x:c r="B61" s="348"/>
+      <x:c r="C61" s="348"/>
+      <x:c r="D61" s="348"/>
+      <x:c r="E61" s="348"/>
+      <x:c r="F61" s="348"/>
+      <x:c r="G61" s="348"/>
+      <x:c r="H61" s="348"/>
+      <x:c r="I61" s="348"/>
+      <x:c r="J61" s="348"/>
+      <x:c r="K61" s="348"/>
+      <x:c r="L61" s="348"/>
+    </x:row>
+    <x:row r="62" ht="28" customHeight="1">
+      <x:c r="A62" s="348"/>
+      <x:c r="B62" s="348"/>
+      <x:c r="C62" s="348"/>
+      <x:c r="D62" s="348"/>
+      <x:c r="E62" s="348"/>
+      <x:c r="F62" s="348"/>
+      <x:c r="G62" s="348"/>
+      <x:c r="H62" s="348"/>
+      <x:c r="I62" s="348"/>
+      <x:c r="J62" s="348"/>
+      <x:c r="K62" s="348"/>
+      <x:c r="L62" s="348"/>
+    </x:row>
+    <x:row r="63" ht="28" customHeight="1">
+      <x:c r="A63" s="348"/>
+      <x:c r="B63" s="348"/>
+      <x:c r="C63" s="348"/>
+      <x:c r="D63" s="348"/>
+      <x:c r="E63" s="348"/>
+      <x:c r="F63" s="348"/>
+      <x:c r="G63" s="348"/>
+      <x:c r="H63" s="348"/>
+      <x:c r="I63" s="348"/>
+      <x:c r="J63" s="348"/>
+      <x:c r="K63" s="348"/>
+      <x:c r="L63" s="348"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A2:N2"/>
-    <x:mergeCell ref="A1:N1"/>
+    <x:mergeCell ref="A1:L1"/>
+    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="A4:L4"/>
+    <x:mergeCell ref="C5:L5"/>
+    <x:mergeCell ref="C6:L6"/>
+    <x:mergeCell ref="C7:L7"/>
+    <x:mergeCell ref="C8:L8"/>
+    <x:mergeCell ref="C9:L9"/>
+    <x:mergeCell ref="C10:L10"/>
+    <x:mergeCell ref="A13:L13"/>
+    <x:mergeCell ref="A24:L24"/>
+    <x:mergeCell ref="A35:L35"/>
+    <x:mergeCell ref="A46:L46"/>
+    <x:mergeCell ref="A55:L55"/>
+    <x:mergeCell ref="B60:L60"/>
+    <x:mergeCell ref="A61:L63"/>
+    <x:mergeCell ref="I40:L40"/>
+    <x:mergeCell ref="B58:L58"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="G49:J51">
+    <x:cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <x:formula>1</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <x:formula>1</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <x:formula>1</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <x:formula>1</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <x:formula>1</x:formula>
+    </x:cfRule>
+    <x:cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="B56">
+      <x:formula1>"MAGH Common Stock,Meridian 4% Bond,Meridian Balanced Fund"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -2730,341 +4434,371 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" customWidth="1"/>
-    <x:col min="2" max="2" width="44" customWidth="1"/>
-    <x:col min="3" max="3" width="44" customWidth="1"/>
-    <x:col min="4" max="4" width="48" customWidth="1"/>
-    <x:col min="5" max="5" width="18" customWidth="1"/>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="38" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="40" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Formula Reference Card - BUS123 MATH-M10-L01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="14" t="n"/>
-      <x:c r="C1" s="14" t="n"/>
-      <x:c r="D1" s="14" t="n"/>
-      <x:c r="E1" s="15" t="n"/>
-    </x:row>
-    <x:row r="2" ht="36" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Use this as a syntax helper after you identify the business question and the required inputs.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" s="14" t="n"/>
-      <x:c r="C2" s="14" t="n"/>
-      <x:c r="D2" s="14" t="n"/>
-      <x:c r="E2" s="15" t="n"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Concept</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Business formula</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Excel syntax pattern</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Example using lesson numbers</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Result</x:t>
-        </x:is>
+      <x:c r="A1" s="318" t="str">
+        <x:v>Formula Reference Card - BUS123 MATH-M10-L01</x:v>
+      </x:c>
+      <x:c r="B1" s="318"/>
+      <x:c r="C1" s="318"/>
+      <x:c r="D1" s="318"/>
+      <x:c r="E1" s="318"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="61" t="str">
+        <x:v>Use this as a syntax helper after you identify the business question and required inputs.</x:v>
+      </x:c>
+      <x:c r="B2" s="61"/>
+      <x:c r="C2" s="61"/>
+      <x:c r="D2" s="61"/>
+      <x:c r="E2" s="61"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="62"/>
+      <x:c r="B3" s="62"/>
+      <x:c r="C3" s="62"/>
+      <x:c r="D3" s="62"/>
+      <x:c r="E3" s="62"/>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="319" t="str">
+        <x:v>Concept</x:v>
+      </x:c>
+      <x:c r="B4" s="319" t="str">
+        <x:v>Business formula</x:v>
+      </x:c>
+      <x:c r="C4" s="319" t="str">
+        <x:v>Excel syntax pattern</x:v>
+      </x:c>
+      <x:c r="D4" s="319" t="str">
+        <x:v>Example using lesson numbers</x:v>
+      </x:c>
+      <x:c r="E4" s="319" t="str">
+        <x:v>Result</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
-      <x:c r="A5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bid-Ask Spread</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Ask Price - Bid Price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="4" t="str">
+      <x:c r="A5" s="64" t="str">
+        <x:v>Bid-Ask Spread</x:v>
+      </x:c>
+      <x:c r="B5" s="65" t="str">
+        <x:v>Ask Price - Bid Price</x:v>
+      </x:c>
+      <x:c r="C5" s="315" t="str">
         <x:v>=Ask_Cell - Bid_Cell</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$39.68 - $39.55</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$0.13</x:t>
-        </x:is>
+      <x:c r="D5" s="65" t="str">
+        <x:v>$39.68 - $39.55</x:v>
+      </x:c>
+      <x:c r="E5" s="67" t="str">
+        <x:v>$0.13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Dividend Yield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual Dividend / Stock Price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" s="4" t="str">
+      <x:c r="A6" s="68" t="str">
+        <x:v>Dividend Yield</x:v>
+      </x:c>
+      <x:c r="B6" s="69" t="str">
+        <x:v>Annual Dividend / Stock Price</x:v>
+      </x:c>
+      <x:c r="C6" s="316" t="str">
         <x:v>=Dividend_Cell / Price_Cell</x:v>
       </x:c>
-      <x:c r="D6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$1.21 / $39.62</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3.05%</x:t>
-        </x:is>
+      <x:c r="D6" s="69" t="str">
+        <x:v>$1.21 / $39.62</x:v>
+      </x:c>
+      <x:c r="E6" s="71" t="str">
+        <x:v>3.05%</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
-      <x:c r="A7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Preferred Dividend Total</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rate x Par Value x Preferred Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" s="4" t="str">
-        <x:v>=Rate_Cell * Par_Cell * Shares_Cell</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8% x $50 x 1,000</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$4,000</x:t>
-        </x:is>
+      <x:c r="A7" s="68" t="str">
+        <x:v>Total Buy Cost</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>Shares x Buy Price x (1 + Commission Rate)</x:v>
+      </x:c>
+      <x:c r="C7" s="316" t="str">
+        <x:v>=Shares * BuyPrice * (1 + Commission)</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>200 x $39.09 x 1.01</x:v>
+      </x:c>
+      <x:c r="E7" s="71" t="str">
+        <x:v>$7,896.18</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
-      <x:c r="A8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Common Dividend/Share</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(Total Dividends - Preferred Dividends) / Common Shares</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" s="4" t="str">
-        <x:v>=(TotalDiv - PrefDiv) / CommonShares</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">($10,000 - $4,000) / 4,000</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$1.50</x:t>
-        </x:is>
+      <x:c r="A8" s="68" t="str">
+        <x:v>Net Sale Proceeds</x:v>
+      </x:c>
+      <x:c r="B8" s="69" t="str">
+        <x:v>Shares x Sale Price x (1 - Commission Rate)</x:v>
+      </x:c>
+      <x:c r="C8" s="316" t="str">
+        <x:v>=Shares * SalePrice * (1 - Commission)</x:v>
+      </x:c>
+      <x:c r="D8" s="69" t="str">
+        <x:v>200 x $41.10 x 0.99</x:v>
+      </x:c>
+      <x:c r="E8" s="71" t="str">
+        <x:v>$8,137.80</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Total Buy Cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares x Buy Price x (1 + Commission Rate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" s="4" t="str">
-        <x:v>=Shares * BuyPrice * (1 + Commission)</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">200 x $39.09 x 1.01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$7,896.18</x:t>
-        </x:is>
+      <x:c r="A9" s="68" t="str">
+        <x:v>ROI</x:v>
+      </x:c>
+      <x:c r="B9" s="69" t="str">
+        <x:v>(Net Proceeds - Total Buy Cost + Dividends) / Total Buy Cost</x:v>
+      </x:c>
+      <x:c r="C9" s="316" t="str">
+        <x:v>=(NetProceeds - BuyCost + Dividends) / BuyCost</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>($8,137.80 - $7,896.18 + $242.00) / $7,896.18</x:v>
+      </x:c>
+      <x:c r="E9" s="71" t="str">
+        <x:v>6.12%</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
-      <x:c r="A10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Net Sale Proceeds</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Shares x Sale Price x (1 - Commission Rate)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" s="4" t="str">
-        <x:v>=Shares * SalePrice * (1 - Commission)</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">200 x $41.10 x 0.99</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$8,137.80</x:t>
-        </x:is>
+      <x:c r="A10" s="68" t="str">
+        <x:v>Bond Dollar Price</x:v>
+      </x:c>
+      <x:c r="B10" s="69" t="str">
+        <x:v>Quoted Price / 100 x Face Value</x:v>
+      </x:c>
+      <x:c r="C10" s="316" t="str">
+        <x:v>=QuotedPrice / 100 * FaceValue</x:v>
+      </x:c>
+      <x:c r="D10" s="69" t="str">
+        <x:v>99.59 / 100 x $1,000</x:v>
+      </x:c>
+      <x:c r="E10" s="71" t="str">
+        <x:v>$995.90</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ROI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(Net Proceeds - Total Buy Cost + Dividends) / Total Buy Cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" s="4" t="str">
-        <x:v>=(NetProceeds - BuyCost + Dividends) / BuyCost</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">($8,137.80 - $7,896.18 + $242.00) / $7,896.18</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6.12%</x:t>
-        </x:is>
+      <x:c r="A11" s="68" t="str">
+        <x:v>Bond Current Yield</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>Annual Interest / Dollar Price</x:v>
+      </x:c>
+      <x:c r="C11" s="316" t="str">
+        <x:v>=AnnualInterest / DollarPrice</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>$40 / $995.90</x:v>
+      </x:c>
+      <x:c r="E11" s="71" t="str">
+        <x:v>4.02%</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
-      <x:c r="A12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bond Dollar Price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Quoted Price / 100 x Face Value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="4" t="str">
-        <x:v>=QuotedPrice / 100 * FaceValue</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">99.59 / 100 x $1,000</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$995.90</x:t>
-        </x:is>
+      <x:c r="A12" s="68" t="str">
+        <x:v>Net Asset Value</x:v>
+      </x:c>
+      <x:c r="B12" s="69" t="str">
+        <x:v>(Holdings - Liabilities) / Shares Outstanding</x:v>
+      </x:c>
+      <x:c r="C12" s="316" t="str">
+        <x:v>=(Holdings - Liabilities) / Shares</x:v>
+      </x:c>
+      <x:c r="D12" s="69" t="str">
+        <x:v>($8,400,000 - $950,000) / 1,200,000</x:v>
+      </x:c>
+      <x:c r="E12" s="71" t="str">
+        <x:v>$6.21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Bond Current Yield</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Annual Interest / Dollar Price</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" s="4" t="str">
-        <x:v>=AnnualInterest / DollarPrice</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$40 / $995.90</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.02%</x:t>
-        </x:is>
+      <x:c r="A13" s="68" t="str">
+        <x:v>Fund Purchase Cost</x:v>
+      </x:c>
+      <x:c r="B13" s="69" t="str">
+        <x:v>Rounded NAV x Shares Purchased</x:v>
+      </x:c>
+      <x:c r="C13" s="316" t="str">
+        <x:v>=ROUND(NAV,2) * SharesToBuy</x:v>
+      </x:c>
+      <x:c r="D13" s="69" t="str">
+        <x:v>$6.21 x 100</x:v>
+      </x:c>
+      <x:c r="E13" s="71" t="str">
+        <x:v>$621.00</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
-      <x:c r="A14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Net Asset Value</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(Holdings - Liabilities) / Shares Outstanding</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" s="4" t="str">
-        <x:v>=(Holdings - Liabilities) / Shares</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">($5,550,000 - $770,000) / 600,000</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$7.97</x:t>
-        </x:is>
+      <x:c r="A14" s="68" t="str">
+        <x:v>Budget Test</x:v>
+      </x:c>
+      <x:c r="B14" s="69" t="str">
+        <x:v>Cost is at or below client budget</x:v>
+      </x:c>
+      <x:c r="C14" s="316" t="str">
+        <x:v>=IF(Cost&lt;=Budget,1,0)</x:v>
+      </x:c>
+      <x:c r="D14" s="69" t="str">
+        <x:v>$4,979.50 &lt;= $8,000</x:v>
+      </x:c>
+      <x:c r="E14" s="71" t="str">
+        <x:v>1 = pass</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
-      <x:c r="A15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fund Purchase Cost</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rounded NAV x Shares Purchased</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" s="4" t="str">
-        <x:v>=ROUND(NAV,2) * SharesToBuy</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$7.97 x 80</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">$637.60</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A15" s="68" t="str">
+        <x:v>Income or Return Test</x:v>
+      </x:c>
+      <x:c r="B15" s="69" t="str">
+        <x:v>Yield meets minimum OR ROI meets minimum</x:v>
+      </x:c>
+      <x:c r="C15" s="316" t="str">
+        <x:v>=IF(OR(Yield&gt;=MinYield,ROI&gt;=MinROI),1,0)</x:v>
+      </x:c>
+      <x:c r="D15" s="69" t="str">
+        <x:v>4.02% &gt;= 4.00%</x:v>
+      </x:c>
+      <x:c r="E15" s="71" t="str">
+        <x:v>1 = pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="68" t="str">
+        <x:v>Risk-Proxy Test</x:v>
+      </x:c>
+      <x:c r="B16" s="69" t="str">
+        <x:v>Creditor priority or diversified pooled fund</x:v>
+      </x:c>
+      <x:c r="C16" s="316" t="str">
+        <x:v>=IF(OR(Type="Bond",Type="Diversified mutual fund"),1,0)</x:v>
+      </x:c>
+      <x:c r="D16" s="69" t="str">
+        <x:v>Bond</x:v>
+      </x:c>
+      <x:c r="E16" s="71" t="str">
+        <x:v>1 = pass</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="72" t="str">
+        <x:v>Overall Eligibility</x:v>
+      </x:c>
+      <x:c r="B17" s="73" t="str">
+        <x:v>Every client constraint passes</x:v>
+      </x:c>
+      <x:c r="C17" s="317" t="str">
+        <x:v>=IF(AND(BudgetTest=1,PerformanceTest=1,RiskTest=1),1,0)</x:v>
+      </x:c>
+      <x:c r="D17" s="73" t="str">
+        <x:v>1 x 1 x 1</x:v>
+      </x:c>
+      <x:c r="E17" s="75" t="str">
+        <x:v>1 = eligible</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="62"/>
+      <x:c r="B18" s="62"/>
+      <x:c r="C18" s="62"/>
+      <x:c r="D18" s="62"/>
+      <x:c r="E18" s="62"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="62"/>
+      <x:c r="B19" s="62"/>
+      <x:c r="C19" s="62"/>
+      <x:c r="D19" s="62"/>
+      <x:c r="E19" s="62"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="62"/>
+      <x:c r="B20" s="62"/>
+      <x:c r="C20" s="62"/>
+      <x:c r="D20" s="62"/>
+      <x:c r="E20" s="62"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="62"/>
+      <x:c r="B21" s="62"/>
+      <x:c r="C21" s="62"/>
+      <x:c r="D21" s="62"/>
+      <x:c r="E21" s="62"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="62"/>
+      <x:c r="B22" s="62"/>
+      <x:c r="C22" s="62"/>
+      <x:c r="D22" s="62"/>
+      <x:c r="E22" s="62"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="62"/>
+      <x:c r="B23" s="62"/>
+      <x:c r="C23" s="62"/>
+      <x:c r="D23" s="62"/>
+      <x:c r="E23" s="62"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="62"/>
+      <x:c r="B24" s="62"/>
+      <x:c r="C24" s="62"/>
+      <x:c r="D24" s="62"/>
+      <x:c r="E24" s="62"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="62"/>
+      <x:c r="B25" s="62"/>
+      <x:c r="C25" s="62"/>
+      <x:c r="D25" s="62"/>
+      <x:c r="E25" s="62"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="62"/>
+      <x:c r="B26" s="62"/>
+      <x:c r="C26" s="62"/>
+      <x:c r="D26" s="62"/>
+      <x:c r="E26" s="62"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="62"/>
+      <x:c r="B27" s="62"/>
+      <x:c r="C27" s="62"/>
+      <x:c r="D27" s="62"/>
+      <x:c r="E27" s="62"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="62"/>
+      <x:c r="B28" s="62"/>
+      <x:c r="C28" s="62"/>
+      <x:c r="D28" s="62"/>
+      <x:c r="E28" s="62"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="62"/>
+      <x:c r="B29" s="62"/>
+      <x:c r="C29" s="62"/>
+      <x:c r="D29" s="62"/>
+      <x:c r="E29" s="62"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="62"/>
+      <x:c r="B30" s="62"/>
+      <x:c r="C30" s="62"/>
+      <x:c r="D30" s="62"/>
+      <x:c r="E30" s="62"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="A2:E2"/>
-    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
